--- a/Kalibrierung_Monitorfaktoren_2025-04-15.xlsx
+++ b/Kalibrierung_Monitorfaktoren_2025-04-15.xlsx
@@ -1,34 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\AG_Neumann\mitarbeiter\Projekte\BASt - Straßenbeleuchtungbedingte Immission\Studienplanung\Versuchsaufbau\Kalibrierung\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\berk\roombrightening\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B12B489-E27F-40C3-90C8-B93B9873AB58}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612799BC-024B-480C-B6CF-0B14C0C0BA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" xr2:uid="{17DC406C-42B8-4956-9234-CDF5DC26EB7C}"/>
+    <workbookView xWindow="1845" yWindow="-15870" windowWidth="25440" windowHeight="15270" activeTab="4" xr2:uid="{17DC406C-42B8-4956-9234-CDF5DC26EB7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
     <sheet name="Tabelle2" sheetId="4" r:id="rId2"/>
     <sheet name="Verhältnis" sheetId="5" r:id="rId3"/>
     <sheet name="Faktoren" sheetId="6" r:id="rId4"/>
+    <sheet name="Berk" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
   <si>
     <t>Spot</t>
   </si>
@@ -86,12 +99,27 @@
   <si>
     <t>Faktoren Gewählt: Mittelwert für E_soll 1, 10 und 31,6lx</t>
   </si>
+  <si>
+    <t>Diffus</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>E_Measured</t>
+  </si>
+  <si>
+    <t>Faktoren Chosen</t>
+  </si>
+  <si>
+    <t>E_ideal</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,6 +138,14 @@
     <font>
       <sz val="11"/>
       <color theme="4" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -170,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -178,11 +214,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="16">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="15" formatCode="0.00E+00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="15" formatCode="0.00E+00"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="15" formatCode="0.00E+00"/>
     </dxf>
@@ -238,7 +292,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -967,7 +1021,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2884,18 +2938,18 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{444C927B-B3AF-481C-857A-898201A32087}" name="Tabelle1" displayName="Tabelle1" ref="A1:F21" totalsRowShown="0">
   <autoFilter ref="A1:F21" xr:uid="{FF6BEAA7-5940-46AB-A3CB-F368572F5FC7}"/>
-  <sortState ref="A2:F21">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F21">
     <sortCondition ref="A1:A21"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{CE91D317-A5E2-4A0B-8E2A-8938EAB5A481}" name="Spot"/>
     <tableColumn id="2" xr3:uid="{70B4DF98-9DF0-4FC5-91CA-8B4B9284CC73}" name="E_soll"/>
-    <tableColumn id="3" xr3:uid="{664CE8FB-7CC3-41BE-8E53-3CCC7057EF9F}" name="A_Monitor" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{664CE8FB-7CC3-41BE-8E53-3CCC7057EF9F}" name="A_Monitor" dataDxfId="15"/>
     <tableColumn id="4" xr3:uid="{86EA1087-BA60-48C7-BD80-4BCBE83FC271}" name="E_Mess"/>
-    <tableColumn id="5" xr3:uid="{07B1D830-407B-4076-A9DB-D9845863EA0B}" name="Faktor" dataDxfId="11">
+    <tableColumn id="5" xr3:uid="{07B1D830-407B-4076-A9DB-D9845863EA0B}" name="Faktor" dataDxfId="14">
       <calculatedColumnFormula>Tabelle1[[#This Row],[E_Mess]]/Tabelle1[[#This Row],[A_Monitor]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{04734A43-203C-4891-84FD-3B432D4339E0}" name="Verhältnis" dataDxfId="10">
+    <tableColumn id="6" xr3:uid="{04734A43-203C-4891-84FD-3B432D4339E0}" name="Verhältnis" dataDxfId="13">
       <calculatedColumnFormula>Tabelle1[[#This Row],[E_Mess]]/Tabelle1[[#This Row],[E_soll]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2908,19 +2962,19 @@
   <autoFilter ref="A1:F5" xr:uid="{7AABCF45-575B-43DC-93F1-BFBAA4EF096E}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{A480BC79-3034-4A0C-BA45-BB2915CE3FD0}" name="E_soll"/>
-    <tableColumn id="2" xr3:uid="{91A9AA42-FA77-4843-8C7A-4DF244A82A9F}" name="Spot1" dataDxfId="9">
+    <tableColumn id="2" xr3:uid="{91A9AA42-FA77-4843-8C7A-4DF244A82A9F}" name="Spot1" dataDxfId="12">
       <calculatedColumnFormula>Tabelle1[[#This Row],[Verhältnis]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{647F10A4-67EC-4255-96C8-B78EBB03032B}" name="Spot2" dataDxfId="8">
+    <tableColumn id="3" xr3:uid="{647F10A4-67EC-4255-96C8-B78EBB03032B}" name="Spot2" dataDxfId="11">
       <calculatedColumnFormula>Tabelle1!F6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{1982D162-1561-4208-8731-8412E5875C4C}" name="Spot3" dataDxfId="7">
+    <tableColumn id="4" xr3:uid="{1982D162-1561-4208-8731-8412E5875C4C}" name="Spot3" dataDxfId="10">
       <calculatedColumnFormula>Tabelle1!F10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{86980F4C-896A-444F-9EC1-C5D35C6DAF15}" name="Spot4" dataDxfId="6">
+    <tableColumn id="5" xr3:uid="{86980F4C-896A-444F-9EC1-C5D35C6DAF15}" name="Spot4" dataDxfId="9">
       <calculatedColumnFormula>Tabelle1!F14</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{28D58D3A-ABE0-4313-800A-6FCA58BCC425}" name="Spot5" dataDxfId="5">
+    <tableColumn id="6" xr3:uid="{28D58D3A-ABE0-4313-800A-6FCA58BCC425}" name="Spot5" dataDxfId="8">
       <calculatedColumnFormula>Tabelle1!F18</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2933,19 +2987,19 @@
   <autoFilter ref="A8:F12" xr:uid="{9DAF4B73-AD35-42AD-82BF-16FFFDFE1FB4}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{BE68D2DF-D45E-45C2-B44C-78938CE226EB}" name="E_soll"/>
-    <tableColumn id="2" xr3:uid="{26AE1C40-4B3B-4327-BCEB-4348F2F9D85C}" name="Faktor 1" dataDxfId="4">
+    <tableColumn id="2" xr3:uid="{26AE1C40-4B3B-4327-BCEB-4348F2F9D85C}" name="Faktor 1" dataDxfId="7">
       <calculatedColumnFormula>Tabelle1!E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{014B1719-C418-4C76-9DC7-B1595725CB39}" name="Faktor 2" dataDxfId="3">
+    <tableColumn id="3" xr3:uid="{014B1719-C418-4C76-9DC7-B1595725CB39}" name="Faktor 2" dataDxfId="6">
       <calculatedColumnFormula>Tabelle1!E6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{85B2697B-F39A-41B3-B84C-7A3072810995}" name="Faktor 3" dataDxfId="2">
+    <tableColumn id="4" xr3:uid="{85B2697B-F39A-41B3-B84C-7A3072810995}" name="Faktor 3" dataDxfId="5">
       <calculatedColumnFormula>Tabelle1!E10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B9FD8C6F-A036-427E-ADC7-ADD6866AE2ED}" name="Faktor 4" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{B9FD8C6F-A036-427E-ADC7-ADD6866AE2ED}" name="Faktor 4" dataDxfId="4">
       <calculatedColumnFormula>Tabelle1!E14</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F33A7BFA-50A4-4664-8608-1069A7E7D710}" name="Faktor 5" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{F33A7BFA-50A4-4664-8608-1069A7E7D710}" name="Faktor 5" dataDxfId="3">
       <calculatedColumnFormula>Tabelle1!E18</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2953,8 +3007,26 @@
 </table>
 </file>
 
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5DC926F9-C1F8-430F-B86A-A779D69972E4}" name="Tabelle15" displayName="Tabelle15" ref="A1:F10" totalsRowShown="0">
+  <autoFilter ref="A1:F10" xr:uid="{FF6BEAA7-5940-46AB-A3CB-F368572F5FC7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F10">
+    <sortCondition ref="A1:A10"/>
+  </sortState>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{3C0CF9E0-6162-486B-B9B3-A301C64146BE}" name="Spot"/>
+    <tableColumn id="2" xr3:uid="{13E9E767-5E06-4E71-AF73-32C115C79686}" name="E_ideal"/>
+    <tableColumn id="3" xr3:uid="{2360E81E-745B-4AF1-ABA7-83BD6FEA5BCF}" name="A_Monitor" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{486B1B0B-2D4D-4ED8-BC6E-35B1AAC7ADE0}" name="E_Measured"/>
+    <tableColumn id="5" xr3:uid="{105A8339-9DC5-40C6-B656-4FB4F9127102}" name="Faktor" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{130CC88C-8630-454C-80FB-C05AD99C988C}" name="Ratio" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3251,7 +3323,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14173062-6BB0-4099-AB05-02EAFE560979}">
   <dimension ref="A1:I24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13.7109375" customWidth="1"/>
   </cols>
@@ -3778,7 +3850,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D58D9505-7494-45E1-9DC8-B366D9CD13E5}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="6" width="13.42578125" customWidth="1"/>
   </cols>
@@ -4030,4 +4102,160 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FB88217-FE2E-45E2-B182-CE8B986A0E10}">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.1</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="H2" s="7">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
+        <f xml:space="preserve"> SUM(E3:E5)/3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="H3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="1">
+        <f xml:space="preserve"> SUM(E7:E9)/3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>31.6</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
+        <v>0.1</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>31.6</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Kalibrierung_Monitorfaktoren_2025-04-15.xlsx
+++ b/Kalibrierung_Monitorfaktoren_2025-04-15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\berk\roombrightening\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612799BC-024B-480C-B6CF-0B14C0C0BA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C1799F-39E4-4321-9D77-3CCC0E0140CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1845" yWindow="-15870" windowWidth="25440" windowHeight="15270" activeTab="4" xr2:uid="{17DC406C-42B8-4956-9234-CDF5DC26EB7C}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>Spot</t>
   </si>
@@ -113,6 +113,18 @@
   </si>
   <si>
     <t>E_ideal</t>
+  </si>
+  <si>
+    <t>Factor</t>
+  </si>
+  <si>
+    <t>Spot 1</t>
+  </si>
+  <si>
+    <t>Max_E  (100% Dimming)</t>
+  </si>
+  <si>
+    <t>Spot 1 (Only Center)</t>
   </si>
 </sst>
 </file>
@@ -206,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -217,11 +229,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3008,18 +3023,22 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5DC926F9-C1F8-430F-B86A-A779D69972E4}" name="Tabelle15" displayName="Tabelle15" ref="A1:F10" totalsRowShown="0">
-  <autoFilter ref="A1:F10" xr:uid="{FF6BEAA7-5940-46AB-A3CB-F368572F5FC7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F10">
-    <sortCondition ref="A1:A10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5DC926F9-C1F8-430F-B86A-A779D69972E4}" name="Tabelle15" displayName="Tabelle15" ref="A1:F9" totalsRowShown="0">
+  <autoFilter ref="A1:F9" xr:uid="{FF6BEAA7-5940-46AB-A3CB-F368572F5FC7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F9">
+    <sortCondition ref="A1:A9"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{3C0CF9E0-6162-486B-B9B3-A301C64146BE}" name="Spot"/>
     <tableColumn id="2" xr3:uid="{13E9E767-5E06-4E71-AF73-32C115C79686}" name="E_ideal"/>
     <tableColumn id="3" xr3:uid="{2360E81E-745B-4AF1-ABA7-83BD6FEA5BCF}" name="A_Monitor" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{486B1B0B-2D4D-4ED8-BC6E-35B1AAC7ADE0}" name="E_Measured"/>
-    <tableColumn id="5" xr3:uid="{105A8339-9DC5-40C6-B656-4FB4F9127102}" name="Faktor" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{130CC88C-8630-454C-80FB-C05AD99C988C}" name="Ratio" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{105A8339-9DC5-40C6-B656-4FB4F9127102}" name="Factor" dataDxfId="1">
+      <calculatedColumnFormula>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{130CC88C-8630-454C-80FB-C05AD99C988C}" name="Ratio" dataDxfId="0">
+      <calculatedColumnFormula>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4106,16 +4125,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FB88217-FE2E-45E2-B182-CE8B986A0E10}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="16.5703125" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
     <col min="9" max="9" width="18.85546875" customWidth="1"/>
+    <col min="11" max="11" width="21.42578125" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4128,131 +4150,241 @@
       <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="H1" s="10" t="s">
         <v>22</v>
       </c>
+      <c r="I1" s="10"/>
+      <c r="K1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="9"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>0.1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="H2" s="7">
+      <c r="C2" s="1">
+        <v>3.9330000000000004E-9</v>
+      </c>
+      <c r="D2">
+        <v>0.1</v>
+      </c>
+      <c r="E2" s="1">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</f>
+        <v>25425883.549453344</v>
+      </c>
+      <c r="F2">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>
         <v>1</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="I2" s="1">
         <f xml:space="preserve"> SUM(E3:E5)/3</f>
-        <v>0</v>
+        <v>24330240.409480657</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2">
+        <v>170.2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="C3" s="1">
+        <v>4.1059999999999998E-8</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</f>
+        <v>24354603.019970775</v>
+      </c>
+      <c r="F3">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>
+        <v>1</v>
+      </c>
       <c r="H3" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I3" s="1">
         <f xml:space="preserve"> SUM(E7:E9)/3</f>
-        <v>0</v>
+        <v>27537654.390823841</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3">
+        <v>434</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4">
         <v>10</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="C4" s="1">
+        <v>4.1189999999999998E-7</v>
+      </c>
+      <c r="D4">
+        <v>10.01</v>
+      </c>
+      <c r="E4" s="1">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</f>
+        <v>24302015.052197136</v>
+      </c>
+      <c r="F4">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>
+        <v>1.0009999999999999</v>
+      </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5">
         <v>31.6</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="C5" s="1">
+        <v>1.299E-6</v>
+      </c>
+      <c r="D5">
+        <v>31.61</v>
+      </c>
+      <c r="E5" s="1">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</f>
+        <v>24334103.156274058</v>
+      </c>
+      <c r="F5">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>
+        <v>1.0003164556962025</v>
+      </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B6">
         <v>0.1</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="C6" s="1">
+        <v>3.476E-9</v>
+      </c>
+      <c r="D6">
+        <v>0.1</v>
+      </c>
+      <c r="E6" s="1">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</f>
+        <v>28768699.654775605</v>
+      </c>
+      <c r="F6">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>
+        <v>1</v>
+      </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="C7" s="1">
+        <v>3.6160000000000001E-8</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</f>
+        <v>27654867.256637167</v>
+      </c>
+      <c r="F7">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B8">
         <v>10</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="C8" s="1">
+        <v>3.6469999999999998E-7</v>
+      </c>
+      <c r="D8">
+        <v>10.01</v>
+      </c>
+      <c r="E8" s="1">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</f>
+        <v>27447216.890595011</v>
+      </c>
+      <c r="F8">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>
+        <v>1.0009999999999999</v>
+      </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B9">
         <v>31.6</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="C9" s="1">
+        <v>1.1489999999999999E-6</v>
+      </c>
+      <c r="D9">
+        <v>31.61</v>
+      </c>
+      <c r="E9" s="1">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</f>
+        <v>27510879.025239341</v>
+      </c>
+      <c r="F9">
+        <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>
+        <v>1.0003164556962025</v>
+      </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C10" s="1"/>
-      <c r="E10" s="1"/>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="H1:I1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/Kalibrierung_Monitorfaktoren_2025-04-15.xlsx
+++ b/Kalibrierung_Monitorfaktoren_2025-04-15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\berk\roombrightening\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C1799F-39E4-4321-9D77-3CCC0E0140CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB000444-8FAF-435E-B643-EAE43061D044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1845" yWindow="-15870" windowWidth="25440" windowHeight="15270" activeTab="4" xr2:uid="{17DC406C-42B8-4956-9234-CDF5DC26EB7C}"/>
+    <workbookView xWindow="5535" yWindow="-10740" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{17DC406C-42B8-4956-9234-CDF5DC26EB7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -4191,13 +4191,13 @@
       </c>
       <c r="I2" s="1">
         <f xml:space="preserve"> SUM(E3:E5)/3</f>
-        <v>24330240.409480657</v>
+        <v>23290759.748018939</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>27</v>
       </c>
       <c r="L2">
-        <v>170.2</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -4208,14 +4208,14 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>4.1059999999999998E-8</v>
+        <v>4.2909999999999998E-8</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" s="1">
         <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</f>
-        <v>24354603.019970775</v>
+        <v>23304591.004427873</v>
       </c>
       <c r="F3">
         <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>
@@ -4226,13 +4226,13 @@
       </c>
       <c r="I3" s="1">
         <f xml:space="preserve"> SUM(E7:E9)/3</f>
-        <v>27537654.390823841</v>
+        <v>27141303.154015142</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>19</v>
       </c>
       <c r="L3">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -4243,14 +4243,14 @@
         <v>10</v>
       </c>
       <c r="C4" s="1">
-        <v>4.1189999999999998E-7</v>
+        <v>4.3010000000000002E-7</v>
       </c>
       <c r="D4">
         <v>10.01</v>
       </c>
       <c r="E4" s="1">
         <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</f>
-        <v>24302015.052197136</v>
+        <v>23273657.289002556</v>
       </c>
       <c r="F4">
         <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>
@@ -4266,14 +4266,14 @@
         <v>31.6</v>
       </c>
       <c r="C5" s="1">
-        <v>1.299E-6</v>
+        <v>1.3570000000000001E-6</v>
       </c>
       <c r="D5">
         <v>31.61</v>
       </c>
       <c r="E5" s="1">
         <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</f>
-        <v>24334103.156274058</v>
+        <v>23294030.950626381</v>
       </c>
       <c r="F5">
         <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>
@@ -4289,14 +4289,14 @@
         <v>0.1</v>
       </c>
       <c r="C6" s="1">
-        <v>3.476E-9</v>
+        <v>3.565E-9</v>
       </c>
       <c r="D6">
         <v>0.1</v>
       </c>
       <c r="E6" s="1">
         <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</f>
-        <v>28768699.654775605</v>
+        <v>28050490.883590464</v>
       </c>
       <c r="F6">
         <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>
@@ -4312,14 +4312,14 @@
         <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>3.6160000000000001E-8</v>
+        <v>3.7009999999999999E-8</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" s="1">
         <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</f>
-        <v>27654867.256637167</v>
+        <v>27019724.398811132</v>
       </c>
       <c r="F7">
         <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>
@@ -4334,14 +4334,14 @@
         <v>10</v>
       </c>
       <c r="C8" s="1">
-        <v>3.6469999999999998E-7</v>
+        <v>3.6800000000000001E-7</v>
       </c>
       <c r="D8">
         <v>10.01</v>
       </c>
       <c r="E8" s="1">
         <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</f>
-        <v>27447216.890595011</v>
+        <v>27201086.956521738</v>
       </c>
       <c r="F8">
         <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>
@@ -4356,14 +4356,14 @@
         <v>31.6</v>
       </c>
       <c r="C9" s="1">
-        <v>1.1489999999999999E-6</v>
+        <v>1.1620000000000001E-6</v>
       </c>
       <c r="D9">
         <v>31.61</v>
       </c>
       <c r="E9" s="1">
         <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[A_Monitor]]</f>
-        <v>27510879.025239341</v>
+        <v>27203098.106712561</v>
       </c>
       <c r="F9">
         <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>

--- a/Kalibrierung_Monitorfaktoren_2025-04-15.xlsx
+++ b/Kalibrierung_Monitorfaktoren_2025-04-15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\berk\roombrightening\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB000444-8FAF-435E-B643-EAE43061D044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F308BC-4046-468E-B11D-CEF7077071FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5535" yWindow="-10740" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{17DC406C-42B8-4956-9234-CDF5DC26EB7C}"/>
+    <workbookView xWindow="2250" yWindow="-14670" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{17DC406C-42B8-4956-9234-CDF5DC26EB7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="29">
   <si>
     <t>Spot</t>
   </si>
@@ -125,6 +125,9 @@
   </si>
   <si>
     <t>Spot 1 (Only Center)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> because of reading light</t>
   </si>
 </sst>
 </file>
@@ -4125,13 +4128,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FB88217-FE2E-45E2-B182-CE8B986A0E10}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="16.5703125" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" customWidth="1"/>
     <col min="6" max="6" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" customWidth="1"/>
     <col min="9" max="9" width="18.85546875" customWidth="1"/>
     <col min="11" max="11" width="21.42578125" customWidth="1"/>
     <col min="12" max="12" width="14.5703125" customWidth="1"/>
@@ -4325,6 +4329,7 @@
         <f>Tabelle15[[#This Row],[E_Measured]]/Tabelle15[[#This Row],[E_ideal]]</f>
         <v>1</v>
       </c>
+      <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
@@ -4378,6 +4383,14 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>8.9999999999999999E-10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
